--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486917_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486917_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1446</v>
+        <v>6.6345</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8429</v>
+        <v>8.125299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6983</v>
+        <v>-1.4908</v>
       </c>
       <c r="G2" t="n">
         <v>3.2229</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.489</v>
+        <v>0.0009</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.178</v>
+        <v>0.1044</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.311</v>
+        <v>-0.1035</v>
       </c>
       <c r="V2" t="n">
         <v>1.7679</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7291</v>
+        <v>3.2607</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5469</v>
+        <v>1.6714</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1822</v>
+        <v>1.5893</v>
       </c>
       <c r="G3" t="n">
         <v>0.9124</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6113</v>
+        <v>1.1429</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3093</v>
+        <v>0.4338</v>
       </c>
       <c r="U3" t="n">
-        <v>1.302</v>
+        <v>0.7091</v>
       </c>
       <c r="V3" t="n">
         <v>0.5893</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3133</v>
+        <v>2.8801</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6398</v>
+        <v>4.5624</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3265</v>
+        <v>-1.6822</v>
       </c>
       <c r="G4" t="n">
         <v>0.9968</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9059</v>
+        <v>0.4727</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5384</v>
+        <v>0.4609</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3675</v>
+        <v>0.0118</v>
       </c>
       <c r="V4" t="n">
         <v>0.5893</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1205</v>
+        <v>-0.3061</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9492</v>
+        <v>-0.2582</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8287</v>
+        <v>-0.0479</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.8592</v>
+        <v>-2.2741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3115</v>
+        <v>-2.5239</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1706</v>
+        <v>0.2498</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4767</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9767</v>
+        <v>-1.2195</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5</v>
+        <v>0.4338</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3358</v>
+        <v>-1.4883</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6653</v>
+        <v>-1.3044</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6706</v>
+        <v>-0.1839</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6736</v>
+        <v>0.3787</v>
       </c>
       <c r="T5" t="n">
-        <v>1.4992</v>
+        <v>0.3756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1744</v>
+        <v>0.003</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.7207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2443</v>
+        <v>-0.8597</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2854</v>
+        <v>-0.031</v>
       </c>
       <c r="F6" t="n">
-        <v>0.041</v>
+        <v>-0.8287</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2741</v>
+        <v>-1.8592</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.5239</v>
+        <v>0.3115</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2498</v>
+        <v>-2.1706</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7858000000000001</v>
+        <v>0.4767</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2195</v>
+        <v>0.9767</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4338</v>
+        <v>-0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4883</v>
+        <v>-2.3358</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3044</v>
+        <v>-0.6653</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1839</v>
+        <v>-1.6706</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4405</v>
+        <v>0.6935</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3485</v>
+        <v>0.5191</v>
       </c>
       <c r="U6" t="n">
-        <v>0.092</v>
+        <v>0.1744</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1786</v>
+        <v>-0.7207</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9811</v>
+        <v>-0.9658</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8708</v>
+        <v>-0.1516</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1104</v>
+        <v>-0.8142</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.8589</v>
+        <v>-1.9035</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8619</v>
+        <v>-1.5085</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.997</v>
+        <v>-0.395</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.6726</v>
+        <v>0.3213</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9753</v>
+        <v>0.0458</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6974</v>
+        <v>0.2755</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1863</v>
+        <v>-2.2248</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1134</v>
+        <v>-1.5543</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2997</v>
+        <v>-0.6706</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8214</v>
+        <v>2.8748</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7074</v>
+        <v>0.0281</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0945</v>
+        <v>-0.0453</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3491</v>
+        <v>-0.9384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3491</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9853</v>
+        <v>-2.2991</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.845</v>
+        <v>-2.3666</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1403</v>
+        <v>0.0675</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9035</v>
+        <v>-3.8589</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5085</v>
+        <v>-1.8619</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.395</v>
+        <v>-1.997</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3213</v>
+        <v>-2.6726</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0458</v>
+        <v>-1.9753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2755</v>
+        <v>-0.6974</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2248</v>
+        <v>-1.1863</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5543</v>
+        <v>0.1134</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6706</v>
+        <v>-1.2997</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.8748</v>
+        <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9915</v>
+        <v>0.3893</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6201</v>
+        <v>0.306</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3714</v>
+        <v>0.0834</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9384</v>
+        <v>0.3491</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1201</v>
+        <v>-3.773</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.033</v>
+        <v>-0.615</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0871</v>
+        <v>-3.158</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.5547</v>
+        <v>-1.1687</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8208</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.7339</v>
+        <v>-0.3314</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2503</v>
+        <v>1.3612</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2107</v>
+        <v>0.7431</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0396</v>
+        <v>0.6181</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3044</v>
+        <v>-2.5298</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6101</v>
+        <v>-1.5804</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6943</v>
+        <v>-0.9495</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3812</v>
+        <v>-0.0417</v>
       </c>
       <c r="T9" t="n">
-        <v>0.244</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1372</v>
+        <v>-0.1189</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1786</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4333</v>
+        <v>-4.0403</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0678</v>
+        <v>-3.0717</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3655</v>
+        <v>-0.9685</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1687</v>
+        <v>-4.5547</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8208</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3314</v>
+        <v>-3.7339</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3612</v>
+        <v>-2.2503</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7431</v>
+        <v>-0.2107</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6181</v>
+        <v>-2.0396</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5298</v>
+        <v>-2.3044</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5804</v>
+        <v>-0.6101</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9495</v>
+        <v>-1.6943</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.702</v>
+        <v>0.461</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3756</v>
+        <v>0.2052</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3264</v>
+        <v>0.2558</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3573</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4566000000000008</v>
+        <v>0.5312999999999981</v>
       </c>
       <c r="E11" t="n">
-        <v>6.876800000000001</v>
+        <v>7.864999999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.3336</v>
+        <v>-7.333499999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-10.487</v>
@@ -1285,25 +1285,25 @@
         <v>-4.0652</v>
       </c>
       <c r="J11" t="n">
-        <v>8.633999999999999</v>
+        <v>8.634</v>
       </c>
       <c r="K11" t="n">
         <v>3.4267</v>
       </c>
       <c r="L11" t="n">
-        <v>5.2072</v>
+        <v>5.207199999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-19.1208</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.848500000000001</v>
+        <v>-9.8485</v>
       </c>
       <c r="O11" t="n">
         <v>-9.272600000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>8.213800000000001</v>
+        <v>8.213799999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-9.2403</v>
@@ -1312,22 +1312,22 @@
         <v>17.4541</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5374</v>
+        <v>3.5254</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5676</v>
+        <v>2.5557</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9698000000000002</v>
+        <v>0.9698</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7207999999999994</v>
+        <v>-0.7208000000000003</v>
       </c>
       <c r="W11" t="n">
-        <v>5.915700000000001</v>
+        <v>5.9157</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.6364</v>
+        <v>-6.636400000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.0344</v>
+        <v>4.4427</v>
       </c>
       <c r="E12" t="n">
-        <v>6.2374</v>
+        <v>4.773</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.203</v>
+        <v>-0.3303</v>
       </c>
       <c r="G12" t="n">
         <v>3.8962</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3444</v>
+        <v>0.7526</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1384</v>
+        <v>0.674</v>
       </c>
       <c r="U12" t="n">
-        <v>0.206</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0.8205</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8472</v>
+        <v>3.5351</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1107</v>
+        <v>4.0061</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2635</v>
+        <v>-0.471</v>
       </c>
       <c r="G13" t="n">
         <v>3.4051</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1833</v>
+        <v>-0.1288</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0541</v>
+        <v>-0.0505</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1292</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1786</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1334</v>
+        <v>2.2886</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9462</v>
+        <v>3.0508</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8127</v>
+        <v>-0.7622</v>
       </c>
       <c r="G14" t="n">
         <v>1.5158</v>
@@ -1546,13 +1546,13 @@
         <v>1.0267</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5745</v>
+        <v>-0.4193</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0118</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5627</v>
+        <v>-0.5121</v>
       </c>
       <c r="V14" t="n">
         <v>1.1922</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6023</v>
+        <v>2.2491</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0783</v>
+        <v>2.4967</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.476</v>
+        <v>-0.2476</v>
       </c>
       <c r="G15" t="n">
         <v>1.4477</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7194</v>
+        <v>-0.0726</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7091</v>
+        <v>-0.2907</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0103</v>
+        <v>0.2181</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3581</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5241</v>
+        <v>1.702</v>
       </c>
       <c r="E16" t="n">
         <v>2.5438</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0197</v>
+        <v>-0.8418</v>
       </c>
       <c r="G16" t="n">
         <v>2.2312</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7687</v>
+        <v>-0.5908</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3216</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.447</v>
+        <v>-0.2692</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3491</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3216</v>
+        <v>1.0277</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.238</v>
+        <v>0.1804</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5596</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="G17" t="n">
         <v>1.9004</v>
@@ -1780,13 +1780,13 @@
         <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9434</v>
+        <v>-0.2373</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5115</v>
+        <v>-0.0931</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4318</v>
+        <v>-0.1442</v>
       </c>
       <c r="V17" t="n">
         <v>2.2394</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.428</v>
+        <v>-0.1908</v>
       </c>
       <c r="E18" t="n">
         <v>-0.3161</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1119</v>
+        <v>0.1253</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9463</v>
@@ -1858,13 +1858,13 @@
         <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.303</v>
+        <v>-0.0659</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3875</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.3216</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2371</v>
+        <v>-3.5928</v>
       </c>
       <c r="E19" t="n">
         <v>-3.2688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0317</v>
+        <v>-0.324</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7517</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.2867</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3798</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4488</v>
+        <v>0.0931</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3491</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.693</v>
+        <v>-4.4541</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3038</v>
+        <v>-3.0946</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3891</v>
+        <v>-1.3595</v>
       </c>
       <c r="G20" t="n">
         <v>0.6339</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.604</v>
+        <v>-0.3651</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3216</v>
+        <v>-0.1124</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2824</v>
+        <v>-0.2527</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6484</v>
+        <v>-5.8534</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4561</v>
+        <v>-3.0377</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1922</v>
+        <v>-2.8156</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8452</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2212</v>
+        <v>-0.4261</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>-0.1008</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7019</v>
+        <v>-0.3253</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2965</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4564999999999992</v>
+        <v>1.154100000000001</v>
       </c>
       <c r="E22" t="n">
         <v>7.3336</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.876799999999999</v>
+        <v>-6.179399999999999</v>
       </c>
       <c r="G22" t="n">
         <v>10.4871</v>
@@ -2170,13 +2170,13 @@
         <v>9.240600000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.5375</v>
+        <v>-1.84</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9696</v>
+        <v>-0.9696000000000002</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5676</v>
+        <v>-0.8702999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.7206999999999999</v>
